--- a/Greg_Woods_Properties_2026.xlsx
+++ b/Greg_Woods_Properties_2026.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTA(Properties!$A$4:$A$1021)</f>
-        <v/>
+        <v>1018</v>
       </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="7" t="inlineStr"/>
@@ -673,7 +673,7 @@
       </c>
       <c r="B6" s="5">
         <f>SUM(Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1157</v>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="7" t="inlineStr"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="B7" s="5">
         <f>SUMPRODUCT(1/COUNTIF(Properties!$C$4:$C$1021,Properties!$C$4:$C$1021))</f>
-        <v/>
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="7" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF(Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>1011</v>
       </c>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="7" t="inlineStr"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF(Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="inlineStr"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Properties!$F$4:$F$1021,"&gt;1")</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="7" t="inlineStr"/>
@@ -789,15 +789,15 @@
       </c>
       <c r="B14" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A14)</f>
-        <v/>
+        <v>226</v>
       </c>
       <c r="C14" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A14,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="D14" s="12">
         <f>B14/$B$5</f>
-        <v/>
+        <v>0.222003929273</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -813,15 +813,15 @@
       </c>
       <c r="B15" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A15)</f>
-        <v/>
+        <v>182</v>
       </c>
       <c r="C15" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A15,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>183</v>
       </c>
       <c r="D15" s="12">
         <f>B15/$B$5</f>
-        <v/>
+        <v>0.178781925344</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -837,15 +837,15 @@
       </c>
       <c r="B16" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A16)</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="C16" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A16,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="D16" s="12">
         <f>B16/$B$5</f>
-        <v/>
+        <v>0.148330058939</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
@@ -861,15 +861,15 @@
       </c>
       <c r="B17" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A17)</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="C17" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A17,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="D17" s="12">
         <f>B17/$B$5</f>
-        <v/>
+        <v>0.08742632613</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
@@ -885,15 +885,15 @@
       </c>
       <c r="B18" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A18)</f>
-        <v/>
+        <v>71</v>
       </c>
       <c r="C18" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A18,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>77</v>
       </c>
       <c r="D18" s="12">
         <f>B18/$B$5</f>
-        <v/>
+        <v>0.06974459725</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -909,15 +909,15 @@
       </c>
       <c r="B19" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A19)</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="C19" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A19,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="D19" s="12">
         <f>B19/$B$5</f>
-        <v/>
+        <v>0.065815324165</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
@@ -933,15 +933,15 @@
       </c>
       <c r="B20" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A20)</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="C20" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A20,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="D20" s="12">
         <f>B20/$B$5</f>
-        <v/>
+        <v>0.036345776031</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
@@ -957,15 +957,15 @@
       </c>
       <c r="B21" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A21)</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="C21" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A21,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="D21" s="12">
         <f>B21/$B$5</f>
-        <v/>
+        <v>0.034381139489</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
@@ -981,15 +981,15 @@
       </c>
       <c r="B22" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A22)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="C22" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A22,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="D22" s="12">
         <f>B22/$B$5</f>
-        <v/>
+        <v>0.020628683694</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
@@ -1005,15 +1005,15 @@
       </c>
       <c r="B23" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A23)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="C23" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A23,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="D23" s="12">
         <f>B23/$B$5</f>
-        <v/>
+        <v>0.020628683694</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
@@ -1029,15 +1029,15 @@
       </c>
       <c r="B24" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A24)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="C24" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A24,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="D24" s="12">
         <f>B24/$B$5</f>
-        <v/>
+        <v>0.019646365422</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
@@ -1053,15 +1053,15 @@
       </c>
       <c r="B25" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A25)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C25" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A25,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D25" s="12">
         <f>B25/$B$5</f>
-        <v/>
+        <v>0.014734774067</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
@@ -1077,15 +1077,15 @@
       </c>
       <c r="B26" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A26)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C26" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A26,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="D26" s="12">
         <f>B26/$B$5</f>
-        <v/>
+        <v>0.012770137525</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -1101,15 +1101,15 @@
       </c>
       <c r="B27" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A27)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C27" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A27,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="D27" s="12">
         <f>B27/$B$5</f>
-        <v/>
+        <v>0.006876227898</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
@@ -1125,15 +1125,15 @@
       </c>
       <c r="B28" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A28)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C28" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A28,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="D28" s="12">
         <f>B28/$B$5</f>
-        <v/>
+        <v>0.006876227898</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -1149,15 +1149,15 @@
       </c>
       <c r="B29" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A29)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C29" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A29,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="D29" s="12">
         <f>B29/$B$5</f>
-        <v/>
+        <v>0.006876227898</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -1173,15 +1173,15 @@
       </c>
       <c r="B30" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A30)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C30" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A30,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="D30" s="12">
         <f>B30/$B$5</f>
-        <v/>
+        <v>0.005893909627</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
@@ -1197,15 +1197,15 @@
       </c>
       <c r="B31" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A31)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C31" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A31,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D31" s="12">
         <f>B31/$B$5</f>
-        <v/>
+        <v>0.005893909627</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -1221,15 +1221,15 @@
       </c>
       <c r="B32" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A32)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C32" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A32,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D32" s="12">
         <f>B32/$B$5</f>
-        <v/>
+        <v>0.005893909627</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -1245,15 +1245,15 @@
       </c>
       <c r="B33" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A33)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C33" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A33,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D33" s="12">
         <f>B33/$B$5</f>
-        <v/>
+        <v>0.005893909627</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -1269,15 +1269,15 @@
       </c>
       <c r="B34" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A34)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C34" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A34,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D34" s="12">
         <f>B34/$B$5</f>
-        <v/>
+        <v>0.003929273084</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -1293,15 +1293,15 @@
       </c>
       <c r="B35" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A35)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C35" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A35,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D35" s="12">
         <f>B35/$B$5</f>
-        <v/>
+        <v>0.002946954813</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
@@ -1317,15 +1317,15 @@
       </c>
       <c r="B36" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A36)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C36" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A36,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D36" s="12">
         <f>B36/$B$5</f>
-        <v/>
+        <v>0.002946954813</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
@@ -1341,15 +1341,15 @@
       </c>
       <c r="B37" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A37)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C37" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A37,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="D37" s="12">
         <f>B37/$B$5</f>
-        <v/>
+        <v>0.002946954813</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -1365,15 +1365,15 @@
       </c>
       <c r="B38" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A38)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C38" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A38,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D38" s="12">
         <f>B38/$B$5</f>
-        <v/>
+        <v>0.002946954813</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
@@ -1389,15 +1389,15 @@
       </c>
       <c r="B39" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A39)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C39" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A39,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D39" s="12">
         <f>B39/$B$5</f>
-        <v/>
+        <v>0.001964636542</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
@@ -1413,15 +1413,15 @@
       </c>
       <c r="B40" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A40)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C40" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A40,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D40" s="12">
         <f>B40/$B$5</f>
-        <v/>
+        <v>0.001964636542</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -1437,15 +1437,15 @@
       </c>
       <c r="B41" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A41)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C41" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A41,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D41" s="12">
         <f>B41/$B$5</f>
-        <v/>
+        <v>0.000982318271</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -1461,15 +1461,15 @@
       </c>
       <c r="B42" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A42)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C42" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A42,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D42" s="12">
         <f>B42/$B$5</f>
-        <v/>
+        <v>0.000982318271</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -1485,15 +1485,15 @@
       </c>
       <c r="B43" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A43)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C43" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A43,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D43" s="12">
         <f>B43/$B$5</f>
-        <v/>
+        <v>0.000982318271</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
@@ -1509,15 +1509,15 @@
       </c>
       <c r="B44" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A44)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C44" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A44,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D44" s="12">
         <f>B44/$B$5</f>
-        <v/>
+        <v>0.000982318271</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -1533,15 +1533,15 @@
       </c>
       <c r="B45" s="11">
         <f>COUNTIF(Properties!$E$4:$E$1021,$A45)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C45" s="11">
         <f>SUMIF(Properties!$E$4:$E$1021,$A45,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D45" s="12">
         <f>B45/$B$5</f>
-        <v/>
+        <v>0.000982318271</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
@@ -1557,15 +1557,15 @@
       </c>
       <c r="B46" s="14">
         <f>SUM(B14:B45)</f>
-        <v/>
+        <v>1018</v>
       </c>
       <c r="C46" s="14">
         <f>SUM(C14:C45)</f>
-        <v/>
+        <v>1157</v>
       </c>
       <c r="D46" s="15">
         <f>SUM(D14:D45)</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="E46" s="16" t="inlineStr"/>
     </row>
@@ -29270,19 +29270,19 @@
       </c>
       <c r="C4" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A4)</f>
-        <v/>
+        <v>226</v>
       </c>
       <c r="D4" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A4,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>250</v>
       </c>
       <c r="E4" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A4,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>226</v>
       </c>
       <c r="F4" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A4,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -29296,19 +29296,19 @@
       </c>
       <c r="C5" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A5)</f>
-        <v/>
+        <v>182</v>
       </c>
       <c r="D5" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A5,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>183</v>
       </c>
       <c r="E5" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A5,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>182</v>
       </c>
       <c r="F5" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A5,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -29322,19 +29322,19 @@
       </c>
       <c r="C6" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A6)</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="D6" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A6,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>174</v>
       </c>
       <c r="E6" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A6,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="F6" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A6,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -29348,19 +29348,19 @@
       </c>
       <c r="C7" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A7)</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="D7" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A7,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>96</v>
       </c>
       <c r="E7" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A7,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>89</v>
       </c>
       <c r="F7" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A7,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -29374,19 +29374,19 @@
       </c>
       <c r="C8" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A8)</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="D8" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A8,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="E8" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A8,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>66</v>
       </c>
       <c r="F8" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A8,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -29400,19 +29400,19 @@
       </c>
       <c r="C9" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A9)</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="D9" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A9,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="E9" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A9,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>43</v>
       </c>
       <c r="F9" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A9,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -29426,19 +29426,19 @@
       </c>
       <c r="C10" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A10)</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="D10" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A10,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="E10" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A10,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="F10" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A10,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -29452,19 +29452,19 @@
       </c>
       <c r="C11" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A11)</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="D11" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A11,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>38</v>
       </c>
       <c r="E11" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A11,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="F11" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A11,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -29478,19 +29478,19 @@
       </c>
       <c r="C12" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A12)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="D12" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A12,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="E12" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A12,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="F12" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A12,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -29504,19 +29504,19 @@
       </c>
       <c r="C13" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A13)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="D13" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A13,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="E13" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A13,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F13" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A13,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -29530,19 +29530,19 @@
       </c>
       <c r="C14" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A14)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="D14" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A14,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="E14" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A14,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F14" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A14,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -29556,19 +29556,19 @@
       </c>
       <c r="C15" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A15)</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="D15" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A15,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="E15" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A15,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>19</v>
       </c>
       <c r="F15" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A15,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -29582,19 +29582,19 @@
       </c>
       <c r="C16" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A16)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="D16" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A16,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="E16" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A16,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="F16" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A16,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -29608,19 +29608,19 @@
       </c>
       <c r="C17" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A17)</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="D17" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A17,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="E17" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A17,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="F17" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A17,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -29634,19 +29634,19 @@
       </c>
       <c r="C18" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A18)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="D18" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A18,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="E18" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A18,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="F18" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A18,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -29660,19 +29660,19 @@
       </c>
       <c r="C19" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A19)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D19" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A19,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="E19" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A19,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F19" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A19,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -29686,19 +29686,19 @@
       </c>
       <c r="C20" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A20)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D20" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A20,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="E20" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A20,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F20" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A20,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -29712,19 +29712,19 @@
       </c>
       <c r="C21" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A21)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D21" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A21,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="E21" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A21,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F21" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A21,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -29738,19 +29738,19 @@
       </c>
       <c r="C22" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A22)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="D22" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A22,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="E22" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A22,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="F22" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A22,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -29764,19 +29764,19 @@
       </c>
       <c r="C23" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A23)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D23" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A23,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="E23" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A23,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F23" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A23,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -29790,19 +29790,19 @@
       </c>
       <c r="C24" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A24)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D24" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A24,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="E24" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A24,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="F24" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A24,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29816,19 +29816,19 @@
       </c>
       <c r="C25" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A25)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="D25" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A25,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="E25" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A25,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="F25" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A25,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -29842,19 +29842,19 @@
       </c>
       <c r="C26" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A26)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D26" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A26,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="E26" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A26,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F26" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A26,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -29868,19 +29868,19 @@
       </c>
       <c r="C27" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A27)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D27" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A27,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E27" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A27,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="F27" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A27,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29894,19 +29894,19 @@
       </c>
       <c r="C28" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A28)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D28" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A28,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="E28" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A28,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F28" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A28,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -29920,19 +29920,19 @@
       </c>
       <c r="C29" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A29)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D29" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A29,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E29" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A29,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F29" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A29,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -29946,19 +29946,19 @@
       </c>
       <c r="C30" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A30)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D30" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A30,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E30" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A30,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="F30" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A30,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29972,19 +29972,19 @@
       </c>
       <c r="C31" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A31)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D31" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A31,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="E31" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A31,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F31" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A31,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -29998,19 +29998,19 @@
       </c>
       <c r="C32" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A32)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D32" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A32,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E32" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A32,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F32" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A32,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -30024,19 +30024,19 @@
       </c>
       <c r="C33" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A33)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D33" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A33,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E33" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A33,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F33" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A33,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -30050,19 +30050,19 @@
       </c>
       <c r="C34" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A34)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D34" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A34,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E34" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A34,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F34" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A34,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -30076,19 +30076,19 @@
       </c>
       <c r="C35" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A35)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D35" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A35,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E35" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A35,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F35" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A35,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -30102,19 +30102,19 @@
       </c>
       <c r="C36" s="11">
         <f>COUNTIF(Properties!$C$4:$C$1021,$A36)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D36" s="11">
         <f>SUMIF(Properties!$C$4:$C$1021,$A36,Properties!$F$4:$F$1021)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E36" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A36,Properties!$B$4:$B$1021,"Commercial")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F36" s="25">
         <f>COUNTIFS(Properties!$C$4:$C$1021,$A36,Properties!$B$4:$B$1021,"Industrial")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30130,19 +30130,19 @@
       </c>
       <c r="C37" s="14">
         <f>SUM(C4:C36)</f>
-        <v/>
+        <v>1018</v>
       </c>
       <c r="D37" s="14">
         <f>SUM(D4:D36)</f>
-        <v/>
+        <v>1157</v>
       </c>
       <c r="E37" s="14">
         <f>SUM(E4:E36)</f>
-        <v/>
+        <v>1011</v>
       </c>
       <c r="F37" s="14">
         <f>SUM(F4:F36)</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
